--- a/примеры/чай-10-сортов.xlsx
+++ b/примеры/чай-10-сортов.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -152,6 +152,30 @@
   </si>
   <si>
     <t>на объём</t>
+  </si>
+  <si>
+    <t>Набор «Чайное путешествие»</t>
+  </si>
+  <si>
+    <t>Наборы</t>
+  </si>
+  <si>
+    <t>Четыре чая для знакомства: чёрный, зелёный жемчуг, травяной и матча. Красивая коробка.</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>Дарджилинг Первый сбор · 50 г×1; Жасминовый жемчуг · 50 г · Пакет×1; Иван-чай ферментированный · 50 г×1; Матча церемониальная · 30 г×1</t>
+  </si>
+  <si>
+    <t>Набор «Утёсный вечер»</t>
+  </si>
+  <si>
+    <t>Улун для неспешного вечера: Да Хун Пао, Те Гуань Инь (100 г) и жасминовый жемчуг в банке.</t>
+  </si>
+  <si>
+    <t>Да Хун Пао · 50 г×1; Те Гуань Инь×100; Жасминовый жемчуг · 50 г · Банка×1</t>
   </si>
 </sst>
 </file>
@@ -532,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1283,8 +1307,90 @@
         <v>100</v>
       </c>
     </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19">
+        <v>1900</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" t="s">
+        <v>51</v>
+      </c>
+      <c r="L19" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20">
+        <v>1500</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>